--- a/data/outputs/sector_attractiveness.xlsx
+++ b/data/outputs/sector_attractiveness.xlsx
@@ -564,7 +564,7 @@
         <v>11148101.06103239</v>
       </c>
       <c r="D2">
-        <v>20921.60484600998</v>
+        <v>20420.85603718308</v>
       </c>
       <c r="E2">
         <v>0.002118934499878127</v>
@@ -579,7 +579,7 @@
         <v>0.09895860007368718</v>
       </c>
       <c r="I2">
-        <v>0.001876696733503822</v>
+        <v>0.001831778876544556</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>100</v>
       </c>
       <c r="X2">
-        <v>0.03035332417062073</v>
+        <v>0.03035011813379622</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -638,7 +638,7 @@
         <v>13487831.27748725</v>
       </c>
       <c r="D3">
-        <v>70034.54270499259</v>
+        <v>68361.82342576774</v>
       </c>
       <c r="E3">
         <v>0.005108022258887793</v>
@@ -653,7 +653,7 @@
         <v>0.1197277360460728</v>
       </c>
       <c r="I3">
-        <v>0.005192424287060022</v>
+        <v>0.005068407368045264</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>99.689097984857</v>
       </c>
       <c r="X3">
-        <v>0.1016069844312749</v>
+        <v>0.1016014908011649</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -712,7 +712,7 @@
         <v>16544740.35864704</v>
       </c>
       <c r="D4">
-        <v>83636.47337916671</v>
+        <v>81638.20659304732</v>
       </c>
       <c r="E4">
         <v>0.005109577392926078</v>
@@ -727,7 +727,7 @@
         <v>0.1468630698188813</v>
       </c>
       <c r="I4">
-        <v>0.005055169894851473</v>
+        <v>0.004934390315190376</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>92.0016164978838</v>
       </c>
       <c r="X4">
-        <v>0.1213408343982508</v>
+        <v>0.1213332687825967</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -786,7 +786,7 @@
         <v>27615980.29119994</v>
       </c>
       <c r="D5">
-        <v>152523.1181706927</v>
+        <v>148883.5101809135</v>
       </c>
       <c r="E5">
         <v>0.005786475883708949</v>
@@ -801,7 +801,7 @@
         <v>0.2451393949802069</v>
       </c>
       <c r="I5">
-        <v>0.005523002137255126</v>
+        <v>0.005391208590497017</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>87.11335935651823</v>
       </c>
       <c r="X5">
-        <v>0.2212824342790248</v>
+        <v>0.2212753527049638</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -860,7 +860,7 @@
         <v>17742449.14435855</v>
       </c>
       <c r="D6">
-        <v>98305.66385668603</v>
+        <v>95963.44596080088</v>
       </c>
       <c r="E6">
         <v>0.005350834438460387</v>
@@ -875,7 +875,7 @@
         <v>0.1574947984048608</v>
       </c>
       <c r="I6">
-        <v>0.005540704276891988</v>
+        <v>0.005408692181108138</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>58.90152260371308</v>
       </c>
       <c r="X6">
-        <v>0.1426230781439854</v>
+        <v>0.1426238898180018</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -934,7 +934,7 @@
         <v>12753198.85762022</v>
       </c>
       <c r="D7">
-        <v>122284.9546254614</v>
+        <v>119373.1685739635</v>
       </c>
       <c r="E7">
         <v>0.008200570620167135</v>
@@ -946,10 +946,10 @@
         <v>1.560674157303371</v>
       </c>
       <c r="H7">
-        <v>0.1132066078789718</v>
+        <v>0.1132066078789719</v>
       </c>
       <c r="I7">
-        <v>0.009588571149143056</v>
+        <v>0.009360253055462729</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>0.09746839736639851</v>
+        <v>0.0974683973663986</v>
       </c>
       <c r="R7">
         <v>0.6525607418606123</v>
@@ -994,7 +994,7 @@
         <v>15.84826278409419</v>
       </c>
       <c r="X7">
-        <v>0.1774125310298152</v>
+        <v>0.1774161554064376</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1008,7 +1008,7 @@
         <v>13361890.28490731</v>
       </c>
       <c r="D8">
-        <v>141562.6242394228</v>
+        <v>138201.7092190425</v>
       </c>
       <c r="E8">
         <v>0.009020761208613131</v>
@@ -1023,7 +1023,7 @@
         <v>0.1186097927973194</v>
       </c>
       <c r="I8">
-        <v>0.01059450580875689</v>
+        <v>0.01034297590178134</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0.205380813547028</v>
+        <v>0.2053997243530389</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_attractiveness.xlsx
+++ b/data/outputs/sector_attractiveness.xlsx
@@ -88,22 +88,22 @@
     <t>ecl_share</t>
   </si>
   <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>agribusiness</t>
+  </si>
+  <si>
+    <t>healthcare</t>
+  </si>
+  <si>
+    <t>utilities</t>
+  </si>
+  <si>
     <t>technology</t>
   </si>
   <si>
-    <t>utilities</t>
-  </si>
-  <si>
-    <t>agribusiness</t>
-  </si>
-  <si>
-    <t>retail</t>
-  </si>
-  <si>
     <t>industry</t>
-  </si>
-  <si>
-    <t>healthcare</t>
   </si>
   <si>
     <t>transport</t>
@@ -558,28 +558,28 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>809</v>
+        <v>1972</v>
       </c>
       <c r="C2">
-        <v>11148101.06103239</v>
+        <v>27612128.92570351</v>
       </c>
       <c r="D2">
-        <v>20420.85603718308</v>
+        <v>46690.29756361964</v>
       </c>
       <c r="E2">
-        <v>0.002118934499878127</v>
+        <v>0.001713220526860417</v>
       </c>
       <c r="F2">
-        <v>0.6894714982691714</v>
+        <v>0.6893616691836554</v>
       </c>
       <c r="G2">
-        <v>1.247218788627936</v>
+        <v>1.269269776876268</v>
       </c>
       <c r="H2">
-        <v>0.09895860007368718</v>
+        <v>0.2451310518128871</v>
       </c>
       <c r="I2">
-        <v>0.001831778876544556</v>
+        <v>0.001690934360376562</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -591,28 +591,28 @@
         <v>31</v>
       </c>
       <c r="M2">
-        <v>0.1986377334611543</v>
+        <v>0.213070727228764</v>
       </c>
       <c r="N2">
-        <v>0.2849365059618074</v>
+        <v>0.5685714536837877</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.4918264579296014</v>
+        <v>0.4403348334095791</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0.5284342653938368</v>
+        <v>0.8685343875409663</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>-0.1530391084985157</v>
+        <v>-0.04633038314258181</v>
       </c>
       <c r="U2">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>100</v>
       </c>
       <c r="X2">
-        <v>0.03035011813379622</v>
+        <v>0.1089659968919541</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -632,28 +632,28 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>976</v>
+        <v>1139</v>
       </c>
       <c r="C3">
-        <v>13487831.27748725</v>
+        <v>16544460.35796101</v>
       </c>
       <c r="D3">
-        <v>68361.82342576774</v>
+        <v>59192.10363793441</v>
       </c>
       <c r="E3">
-        <v>0.005108022258887793</v>
+        <v>0.003794104472979617</v>
       </c>
       <c r="F3">
-        <v>0.6898398724708215</v>
+        <v>0.687074752583591</v>
       </c>
       <c r="G3">
-        <v>1.360655737704918</v>
+        <v>1.287093942054434</v>
       </c>
       <c r="H3">
-        <v>0.1197277360460728</v>
+        <v>0.1468760695756554</v>
       </c>
       <c r="I3">
-        <v>0.005068407368045264</v>
+        <v>0.003577759706707618</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -665,28 +665,28 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>0.2019839570023267</v>
+        <v>0.2036201992634756</v>
       </c>
       <c r="N3">
-        <v>-0.1557643802749924</v>
+        <v>0.5278061963378733</v>
       </c>
       <c r="O3">
-        <v>0.433086469010683</v>
+        <v>0.4604090806316603</v>
       </c>
       <c r="P3">
-        <v>0.577942445712717</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.1420784172480873</v>
+        <v>0.3278115574106878</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.8196537079418696</v>
       </c>
       <c r="S3">
-        <v>0.2077088020403448</v>
+        <v>0.2901414062795252</v>
       </c>
       <c r="T3">
-        <v>-0.153962106084688</v>
+        <v>-0.2001796380769411</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -695,10 +695,10 @@
         <v>32</v>
       </c>
       <c r="W3">
-        <v>99.689097984857</v>
+        <v>55.54229810662171</v>
       </c>
       <c r="X3">
-        <v>0.1016014908011649</v>
+        <v>0.1381427602223094</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -706,28 +706,28 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>1139</v>
+        <v>890</v>
       </c>
       <c r="C4">
-        <v>16544740.35864704</v>
+        <v>12752907.34577825</v>
       </c>
       <c r="D4">
-        <v>81638.20659304732</v>
+        <v>34882.611540844</v>
       </c>
       <c r="E4">
-        <v>0.005109577392926078</v>
+        <v>0.003022402970105342</v>
       </c>
       <c r="F4">
-        <v>0.6873676359846619</v>
+        <v>0.6909440643754788</v>
       </c>
       <c r="G4">
-        <v>1.377524143985953</v>
+        <v>1.265168539325843</v>
       </c>
       <c r="H4">
-        <v>0.1468630698188813</v>
+        <v>0.1132159566455185</v>
       </c>
       <c r="I4">
-        <v>0.004934390315190376</v>
+        <v>0.00273526738609856</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -739,28 +739,28 @@
         <v>31</v>
       </c>
       <c r="M4">
-        <v>0.2042036651359909</v>
+        <v>0.2007193697276898</v>
       </c>
       <c r="N4">
-        <v>0.5278061963378733</v>
+        <v>0.3884548653240452</v>
       </c>
       <c r="O4">
-        <v>0.4333117911035017</v>
+        <v>0.2896651138078312</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.7450174454296572</v>
       </c>
       <c r="Q4">
-        <v>0.3277069999231312</v>
+        <v>0.09753378041959387</v>
       </c>
       <c r="R4">
-        <v>0.8196537079418696</v>
+        <v>0.6525607418606123</v>
       </c>
       <c r="S4">
-        <v>0.345491861554974</v>
+        <v>0.07225106380775075</v>
       </c>
       <c r="T4">
-        <v>-0.1767844954891333</v>
+        <v>-0.2750077544661121</v>
       </c>
       <c r="U4">
         <v>3</v>
@@ -769,10 +769,10 @@
         <v>33</v>
       </c>
       <c r="W4">
-        <v>92.0016164978838</v>
+        <v>33.91927436762389</v>
       </c>
       <c r="X4">
-        <v>0.1213332687825967</v>
+        <v>0.08140917362035714</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -780,28 +780,28 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>1972</v>
+        <v>976</v>
       </c>
       <c r="C5">
-        <v>27615980.29119994</v>
+        <v>13488381.37391186</v>
       </c>
       <c r="D5">
-        <v>148883.5101809135</v>
+        <v>94422.09484959475</v>
       </c>
       <c r="E5">
-        <v>0.005786475883708949</v>
+        <v>0.006232861936331147</v>
       </c>
       <c r="F5">
-        <v>0.6895968543224502</v>
+        <v>0.6905296766388008</v>
       </c>
       <c r="G5">
-        <v>1.342292089249493</v>
+        <v>1.450819672131147</v>
       </c>
       <c r="H5">
-        <v>0.2451393949802069</v>
+        <v>0.1197452439229522</v>
       </c>
       <c r="I5">
-        <v>0.005391208590497017</v>
+        <v>0.007000253939454762</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -813,28 +813,28 @@
         <v>31</v>
       </c>
       <c r="M5">
-        <v>0.2147479007159943</v>
+        <v>0.2025736044945878</v>
       </c>
       <c r="N5">
-        <v>0.5685714536837877</v>
+        <v>-0.1557643802749924</v>
       </c>
       <c r="O5">
-        <v>0.5313870571669315</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>0.5211313340700637</v>
+        <v>0.6652290723023007</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.1422023696992656</v>
       </c>
       <c r="R5">
-        <v>0.8685343875409663</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0.2115284130619332</v>
       </c>
       <c r="T5">
-        <v>-0.1912966225333874</v>
+        <v>-0.307656192381655</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -843,10 +843,10 @@
         <v>33</v>
       </c>
       <c r="W5">
-        <v>87.11335935651823</v>
+        <v>24.484880156531</v>
       </c>
       <c r="X5">
-        <v>0.2212753527049638</v>
+        <v>0.2203626498608912</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -854,28 +854,28 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>1271</v>
+        <v>809</v>
       </c>
       <c r="C6">
-        <v>17742449.14435855</v>
+        <v>11147001.19290712</v>
       </c>
       <c r="D6">
-        <v>95963.44596080088</v>
+        <v>49601.3950815514</v>
       </c>
       <c r="E6">
-        <v>0.005350834438460387</v>
+        <v>0.004945577544790887</v>
       </c>
       <c r="F6">
-        <v>0.6897019629952355</v>
+        <v>0.6894165745275845</v>
       </c>
       <c r="G6">
-        <v>1.313139260424862</v>
+        <v>1.316440049443758</v>
       </c>
       <c r="H6">
-        <v>0.1574947984048608</v>
+        <v>0.09895927019351372</v>
       </c>
       <c r="I6">
-        <v>0.005408692181108138</v>
+        <v>0.004449752379421378</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -887,28 +887,28 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>0.2058302062149173</v>
+        <v>0.1997574729427846</v>
       </c>
       <c r="N6">
-        <v>0.6782104678706893</v>
+        <v>0.2849365059618074</v>
       </c>
       <c r="O6">
-        <v>0.4682673261691638</v>
+        <v>0.7151799722777107</v>
       </c>
       <c r="P6">
-        <v>0.5457029168272954</v>
+        <v>0.4509065943000549</v>
       </c>
       <c r="Q6">
-        <v>0.4004369956300114</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0.5284342653938368</v>
       </c>
       <c r="S6">
-        <v>0.4464554985673522</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>-0.2750511688406814</v>
+        <v>-0.3256961220235114</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -917,10 +917,10 @@
         <v>33</v>
       </c>
       <c r="W6">
-        <v>58.90152260371308</v>
+        <v>19.27189544277756</v>
       </c>
       <c r="X6">
-        <v>0.1426238898180018</v>
+        <v>0.1157599275294468</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -928,28 +928,28 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>890</v>
+        <v>1271</v>
       </c>
       <c r="C7">
-        <v>12753198.85762022</v>
+        <v>17738299.12155825</v>
       </c>
       <c r="D7">
-        <v>119373.1685739635</v>
+        <v>94367.40951191922</v>
       </c>
       <c r="E7">
-        <v>0.008200570620167135</v>
+        <v>0.004872875091881172</v>
       </c>
       <c r="F7">
-        <v>0.6916452876859672</v>
+        <v>0.6900363533654161</v>
       </c>
       <c r="G7">
-        <v>1.560674157303371</v>
+        <v>1.280881195908733</v>
       </c>
       <c r="H7">
-        <v>0.1132066078789719</v>
+        <v>0.1574745624554699</v>
       </c>
       <c r="I7">
-        <v>0.009360253055462729</v>
+        <v>0.005319980730127036</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -961,28 +961,28 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>0.2029299465731575</v>
+        <v>0.2057038769553827</v>
       </c>
       <c r="N7">
-        <v>0.3884548653240452</v>
+        <v>0.6782104678706893</v>
       </c>
       <c r="O7">
-        <v>0.8811632596616841</v>
+        <v>0.6990940826411192</v>
       </c>
       <c r="P7">
+        <v>0.5702420398076313</v>
+      </c>
+      <c r="Q7">
+        <v>0.4003186635182989</v>
+      </c>
+      <c r="R7">
         <v>1</v>
       </c>
-      <c r="Q7">
-        <v>0.0974683973663986</v>
-      </c>
-      <c r="R7">
-        <v>0.6525607418606123</v>
-      </c>
       <c r="S7">
-        <v>0.2664288361570978</v>
+        <v>0.4466529283422783</v>
       </c>
       <c r="T7">
-        <v>-0.4028665349523433</v>
+        <v>-0.3363617476564859</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -991,10 +991,10 @@
         <v>34</v>
       </c>
       <c r="W7">
-        <v>15.84826278409419</v>
+        <v>16.18985773580615</v>
       </c>
       <c r="X7">
-        <v>0.1774161554064376</v>
+        <v>0.2202350250084887</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1005,25 +1005,25 @@
         <v>943</v>
       </c>
       <c r="C8">
-        <v>13361890.28490731</v>
+        <v>13359135.74845482</v>
       </c>
       <c r="D8">
-        <v>138201.7092190425</v>
+        <v>49329.10970550036</v>
       </c>
       <c r="E8">
-        <v>0.009020761208613131</v>
+        <v>0.003953842396188018</v>
       </c>
       <c r="F8">
-        <v>0.6909876265486031</v>
+        <v>0.6922683380702455</v>
       </c>
       <c r="G8">
-        <v>1.542948038176034</v>
+        <v>1.250265111346766</v>
       </c>
       <c r="H8">
-        <v>0.1186097927973194</v>
+        <v>0.1185978453940032</v>
       </c>
       <c r="I8">
-        <v>0.01034297590178134</v>
+        <v>0.003692537499007449</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1035,28 +1035,28 @@
         <v>31</v>
       </c>
       <c r="M8">
-        <v>0.2036668090728978</v>
+        <v>0.2018949891119246</v>
       </c>
       <c r="N8">
         <v>0.6585491754669682</v>
       </c>
       <c r="O8">
+        <v>0.4957521330414547</v>
+      </c>
+      <c r="P8">
         <v>1</v>
       </c>
-      <c r="P8">
-        <v>0.8462565016306941</v>
-      </c>
       <c r="Q8">
-        <v>0.1344307419876795</v>
+        <v>0.1343527114667572</v>
       </c>
       <c r="R8">
         <v>0.9764245978791358</v>
       </c>
       <c r="S8">
-        <v>0.3121678088247439</v>
+        <v>0.160555497793735</v>
       </c>
       <c r="T8">
-        <v>-0.4499164335772032</v>
+        <v>-0.3923879803241271</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0.2053997243530389</v>
+        <v>0.1151244668665527</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_attractiveness.xlsx
+++ b/data/outputs/sector_attractiveness.xlsx
@@ -88,22 +88,22 @@
     <t>ecl_share</t>
   </si>
   <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>utilities</t>
+  </si>
+  <si>
+    <t>agribusiness</t>
+  </si>
+  <si>
     <t>retail</t>
   </si>
   <si>
-    <t>agribusiness</t>
+    <t>industry</t>
   </si>
   <si>
     <t>healthcare</t>
-  </si>
-  <si>
-    <t>utilities</t>
-  </si>
-  <si>
-    <t>technology</t>
-  </si>
-  <si>
-    <t>industry</t>
   </si>
   <si>
     <t>transport</t>
@@ -558,28 +558,28 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>1972</v>
+        <v>809</v>
       </c>
       <c r="C2">
-        <v>27612128.92570351</v>
+        <v>11148101.06103239</v>
       </c>
       <c r="D2">
-        <v>46690.29756361964</v>
+        <v>20420.85603718308</v>
       </c>
       <c r="E2">
-        <v>0.001713220526860417</v>
+        <v>0.002118934499878127</v>
       </c>
       <c r="F2">
-        <v>0.6893616691836554</v>
+        <v>0.6894714982691714</v>
       </c>
       <c r="G2">
-        <v>1.269269776876268</v>
+        <v>1.247218788627936</v>
       </c>
       <c r="H2">
-        <v>0.2451310518128871</v>
+        <v>0.09895860007368718</v>
       </c>
       <c r="I2">
-        <v>0.001690934360376562</v>
+        <v>0.001831778876544556</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -591,28 +591,28 @@
         <v>31</v>
       </c>
       <c r="M2">
-        <v>0.213070727228764</v>
+        <v>0.1986377334611543</v>
       </c>
       <c r="N2">
-        <v>0.5685714536837877</v>
+        <v>0.2849365059618074</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.4403348334095791</v>
+        <v>0.4918264579295886</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.8685343875409663</v>
+        <v>0.5284342653938368</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-0.04633038314258181</v>
+        <v>-0.1530391084985138</v>
       </c>
       <c r="U2">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>100</v>
       </c>
       <c r="X2">
-        <v>0.1089659968919541</v>
+        <v>0.03035011813379622</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -632,28 +632,28 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>1139</v>
+        <v>976</v>
       </c>
       <c r="C3">
-        <v>16544460.35796101</v>
+        <v>13487831.27748725</v>
       </c>
       <c r="D3">
-        <v>59192.10363793441</v>
+        <v>68361.82342576774</v>
       </c>
       <c r="E3">
-        <v>0.003794104472979617</v>
+        <v>0.005108022258887793</v>
       </c>
       <c r="F3">
-        <v>0.687074752583591</v>
+        <v>0.6898398724708215</v>
       </c>
       <c r="G3">
-        <v>1.287093942054434</v>
+        <v>1.360655737704918</v>
       </c>
       <c r="H3">
-        <v>0.1468760695756554</v>
+        <v>0.1197277360460728</v>
       </c>
       <c r="I3">
-        <v>0.003577759706707618</v>
+        <v>0.005068407368045264</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -665,28 +665,28 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>0.2036201992634756</v>
+        <v>0.2019839570023267</v>
       </c>
       <c r="N3">
-        <v>0.5278061963378733</v>
+        <v>-0.1557643802749924</v>
       </c>
       <c r="O3">
-        <v>0.4604090806316603</v>
+        <v>0.433086469010683</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.577942445712702</v>
       </c>
       <c r="Q3">
-        <v>0.3278115574106878</v>
+        <v>0.1420784172480873</v>
       </c>
       <c r="R3">
-        <v>0.8196537079418696</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.2901414062795252</v>
+        <v>0.2077088020403448</v>
       </c>
       <c r="T3">
-        <v>-0.2001796380769411</v>
+        <v>-0.1539621060846857</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -695,10 +695,10 @@
         <v>32</v>
       </c>
       <c r="W3">
-        <v>55.54229810662171</v>
+        <v>99.68909798485711</v>
       </c>
       <c r="X3">
-        <v>0.1381427602223094</v>
+        <v>0.1016014908011649</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -706,28 +706,28 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>890</v>
+        <v>1139</v>
       </c>
       <c r="C4">
-        <v>12752907.34577825</v>
+        <v>16544740.35864704</v>
       </c>
       <c r="D4">
-        <v>34882.611540844</v>
+        <v>81638.20659304732</v>
       </c>
       <c r="E4">
-        <v>0.003022402970105342</v>
+        <v>0.005109577392926078</v>
       </c>
       <c r="F4">
-        <v>0.6909440643754788</v>
+        <v>0.6873676359846619</v>
       </c>
       <c r="G4">
-        <v>1.265168539325843</v>
+        <v>1.377524143985953</v>
       </c>
       <c r="H4">
-        <v>0.1132159566455185</v>
+        <v>0.1468630698188813</v>
       </c>
       <c r="I4">
-        <v>0.00273526738609856</v>
+        <v>0.004934390315190376</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -739,28 +739,28 @@
         <v>31</v>
       </c>
       <c r="M4">
-        <v>0.2007193697276898</v>
+        <v>0.2042036651359909</v>
       </c>
       <c r="N4">
-        <v>0.3884548653240452</v>
+        <v>0.5278061963378733</v>
       </c>
       <c r="O4">
-        <v>0.2896651138078312</v>
+        <v>0.4333117911035017</v>
       </c>
       <c r="P4">
-        <v>0.7450174454296572</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.09753378041959387</v>
+        <v>0.3277069999231312</v>
       </c>
       <c r="R4">
-        <v>0.6525607418606123</v>
+        <v>0.8196537079418696</v>
       </c>
       <c r="S4">
-        <v>0.07225106380775075</v>
+        <v>0.345491861554974</v>
       </c>
       <c r="T4">
-        <v>-0.2750077544661121</v>
+        <v>-0.1767844954891333</v>
       </c>
       <c r="U4">
         <v>3</v>
@@ -769,10 +769,10 @@
         <v>33</v>
       </c>
       <c r="W4">
-        <v>33.91927436762389</v>
+        <v>92.00161649788313</v>
       </c>
       <c r="X4">
-        <v>0.08140917362035714</v>
+        <v>0.1213332687825967</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -780,28 +780,28 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>976</v>
+        <v>1972</v>
       </c>
       <c r="C5">
-        <v>13488381.37391186</v>
+        <v>27615980.29119994</v>
       </c>
       <c r="D5">
-        <v>94422.09484959475</v>
+        <v>148883.5101809135</v>
       </c>
       <c r="E5">
-        <v>0.006232861936331147</v>
+        <v>0.005786475883708949</v>
       </c>
       <c r="F5">
-        <v>0.6905296766388008</v>
+        <v>0.6895968543224502</v>
       </c>
       <c r="G5">
-        <v>1.450819672131147</v>
+        <v>1.342292089249493</v>
       </c>
       <c r="H5">
-        <v>0.1197452439229522</v>
+        <v>0.2451393949802069</v>
       </c>
       <c r="I5">
-        <v>0.007000253939454762</v>
+        <v>0.005391208590497017</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -813,28 +813,28 @@
         <v>31</v>
       </c>
       <c r="M5">
-        <v>0.2025736044945878</v>
+        <v>0.2147479007159943</v>
       </c>
       <c r="N5">
-        <v>-0.1557643802749924</v>
+        <v>0.5685714536837877</v>
       </c>
       <c r="O5">
+        <v>0.5313870571669315</v>
+      </c>
+      <c r="P5">
+        <v>0.5211313340700503</v>
+      </c>
+      <c r="Q5">
         <v>1</v>
       </c>
-      <c r="P5">
-        <v>0.6652290723023007</v>
-      </c>
-      <c r="Q5">
-        <v>0.1422023696992656</v>
-      </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.8685343875409663</v>
       </c>
       <c r="S5">
-        <v>0.2115284130619332</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>-0.307656192381655</v>
+        <v>-0.1912966225333854</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -843,10 +843,10 @@
         <v>33</v>
       </c>
       <c r="W5">
-        <v>24.484880156531</v>
+        <v>87.1133593565182</v>
       </c>
       <c r="X5">
-        <v>0.2203626498608912</v>
+        <v>0.2212753527049638</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -854,28 +854,28 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>809</v>
+        <v>1271</v>
       </c>
       <c r="C6">
-        <v>11147001.19290712</v>
+        <v>17742449.14435855</v>
       </c>
       <c r="D6">
-        <v>49601.3950815514</v>
+        <v>95963.44596080088</v>
       </c>
       <c r="E6">
-        <v>0.004945577544790887</v>
+        <v>0.005350834438460387</v>
       </c>
       <c r="F6">
-        <v>0.6894165745275845</v>
+        <v>0.6897019629952355</v>
       </c>
       <c r="G6">
-        <v>1.316440049443758</v>
+        <v>1.313139260424862</v>
       </c>
       <c r="H6">
-        <v>0.09895927019351372</v>
+        <v>0.1574947984048608</v>
       </c>
       <c r="I6">
-        <v>0.004449752379421378</v>
+        <v>0.005408692181108138</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -887,28 +887,28 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>0.1997574729427846</v>
+        <v>0.2058302062149173</v>
       </c>
       <c r="N6">
-        <v>0.2849365059618074</v>
+        <v>0.6782104678706893</v>
       </c>
       <c r="O6">
-        <v>0.7151799722777107</v>
+        <v>0.4682673261691638</v>
       </c>
       <c r="P6">
-        <v>0.4509065943000549</v>
+        <v>0.5457029168272812</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>0.4004369956300114</v>
       </c>
       <c r="R6">
-        <v>0.5284342653938368</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.4464554985673522</v>
       </c>
       <c r="T6">
-        <v>-0.3256961220235114</v>
+        <v>-0.2750511688406791</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -917,10 +917,10 @@
         <v>33</v>
       </c>
       <c r="W6">
-        <v>19.27189544277756</v>
+        <v>58.901522603713</v>
       </c>
       <c r="X6">
-        <v>0.1157599275294468</v>
+        <v>0.1426238898180018</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -928,28 +928,28 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>1271</v>
+        <v>890</v>
       </c>
       <c r="C7">
-        <v>17738299.12155825</v>
+        <v>12753198.85762022</v>
       </c>
       <c r="D7">
-        <v>94367.40951191922</v>
+        <v>119373.1685739635</v>
       </c>
       <c r="E7">
-        <v>0.004872875091881172</v>
+        <v>0.008200570620167135</v>
       </c>
       <c r="F7">
-        <v>0.6900363533654161</v>
+        <v>0.6916452876859673</v>
       </c>
       <c r="G7">
-        <v>1.280881195908733</v>
+        <v>1.560674157303371</v>
       </c>
       <c r="H7">
-        <v>0.1574745624554699</v>
+        <v>0.1132066078789718</v>
       </c>
       <c r="I7">
-        <v>0.005319980730127036</v>
+        <v>0.009360253055462731</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -961,28 +961,28 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>0.2057038769553827</v>
+        <v>0.2029299465731575</v>
       </c>
       <c r="N7">
-        <v>0.6782104678706893</v>
+        <v>0.3884548653240452</v>
       </c>
       <c r="O7">
-        <v>0.6990940826411192</v>
+        <v>0.8811632596616841</v>
       </c>
       <c r="P7">
-        <v>0.5702420398076313</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>0.4003186635182989</v>
+        <v>0.09746839736639851</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0.6525607418606123</v>
       </c>
       <c r="S7">
-        <v>0.4466529283422783</v>
+        <v>0.2664288361570978</v>
       </c>
       <c r="T7">
-        <v>-0.3363617476564859</v>
+        <v>-0.4028665349523433</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -991,10 +991,10 @@
         <v>34</v>
       </c>
       <c r="W7">
-        <v>16.18985773580615</v>
+        <v>15.84826278409318</v>
       </c>
       <c r="X7">
-        <v>0.2202350250084887</v>
+        <v>0.1774161554064376</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1005,25 +1005,25 @@
         <v>943</v>
       </c>
       <c r="C8">
-        <v>13359135.74845482</v>
+        <v>13361890.28490731</v>
       </c>
       <c r="D8">
-        <v>49329.10970550036</v>
+        <v>138201.7092190425</v>
       </c>
       <c r="E8">
-        <v>0.003953842396188018</v>
+        <v>0.009020761208613131</v>
       </c>
       <c r="F8">
-        <v>0.6922683380702455</v>
+        <v>0.6909876265486031</v>
       </c>
       <c r="G8">
-        <v>1.250265111346766</v>
+        <v>1.542948038176034</v>
       </c>
       <c r="H8">
-        <v>0.1185978453940032</v>
+        <v>0.1186097927973194</v>
       </c>
       <c r="I8">
-        <v>0.003692537499007449</v>
+        <v>0.01034297590178134</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1035,28 +1035,28 @@
         <v>31</v>
       </c>
       <c r="M8">
-        <v>0.2018949891119246</v>
+        <v>0.2036668090728978</v>
       </c>
       <c r="N8">
         <v>0.6585491754669682</v>
       </c>
       <c r="O8">
-        <v>0.4957521330414547</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0.8462565016306721</v>
       </c>
       <c r="Q8">
-        <v>0.1343527114667572</v>
+        <v>0.1344307419876795</v>
       </c>
       <c r="R8">
         <v>0.9764245978791358</v>
       </c>
       <c r="S8">
-        <v>0.160555497793735</v>
+        <v>0.3121678088247439</v>
       </c>
       <c r="T8">
-        <v>-0.3923879803241271</v>
+        <v>-0.4499164335772</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0.1151244668665527</v>
+        <v>0.2053997243530389</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_attractiveness.xlsx
+++ b/data/outputs/sector_attractiveness.xlsx
@@ -88,22 +88,22 @@
     <t>ecl_share</t>
   </si>
   <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>agribusiness</t>
+  </si>
+  <si>
+    <t>healthcare</t>
+  </si>
+  <si>
+    <t>utilities</t>
+  </si>
+  <si>
     <t>technology</t>
   </si>
   <si>
-    <t>utilities</t>
-  </si>
-  <si>
-    <t>agribusiness</t>
-  </si>
-  <si>
-    <t>retail</t>
-  </si>
-  <si>
     <t>industry</t>
-  </si>
-  <si>
-    <t>healthcare</t>
   </si>
   <si>
     <t>transport</t>
@@ -558,28 +558,28 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>809</v>
+        <v>1972</v>
       </c>
       <c r="C2">
-        <v>11148101.06103239</v>
+        <v>27612128.92570351</v>
       </c>
       <c r="D2">
-        <v>20420.85603718308</v>
+        <v>46690.29756361964</v>
       </c>
       <c r="E2">
-        <v>0.002118934499878127</v>
+        <v>0.001713220526860417</v>
       </c>
       <c r="F2">
-        <v>0.6894714982691714</v>
+        <v>0.6893616691836554</v>
       </c>
       <c r="G2">
-        <v>1.247218788627936</v>
+        <v>1.269269776876268</v>
       </c>
       <c r="H2">
-        <v>0.09895860007368718</v>
+        <v>0.2451310518128871</v>
       </c>
       <c r="I2">
-        <v>0.001831778876544556</v>
+        <v>0.001690934360376562</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -591,28 +591,28 @@
         <v>31</v>
       </c>
       <c r="M2">
-        <v>0.1986377334611543</v>
+        <v>0.213070727228764</v>
       </c>
       <c r="N2">
-        <v>0.2849365059618074</v>
+        <v>0.5685714536837877</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.4918264579295886</v>
+        <v>0.4403348334095791</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0.5284342653938368</v>
+        <v>0.8685343875409663</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>-0.1530391084985138</v>
+        <v>-0.04633038314258181</v>
       </c>
       <c r="U2">
         <v>1</v>
@@ -624,7 +624,7 @@
         <v>100</v>
       </c>
       <c r="X2">
-        <v>0.03035011813379622</v>
+        <v>0.1089659968919541</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -632,28 +632,28 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>976</v>
+        <v>1139</v>
       </c>
       <c r="C3">
-        <v>13487831.27748725</v>
+        <v>16544460.35796101</v>
       </c>
       <c r="D3">
-        <v>68361.82342576774</v>
+        <v>59192.10363793441</v>
       </c>
       <c r="E3">
-        <v>0.005108022258887793</v>
+        <v>0.003794104472979617</v>
       </c>
       <c r="F3">
-        <v>0.6898398724708215</v>
+        <v>0.687074752583591</v>
       </c>
       <c r="G3">
-        <v>1.360655737704918</v>
+        <v>1.287093942054434</v>
       </c>
       <c r="H3">
-        <v>0.1197277360460728</v>
+        <v>0.1468760695756554</v>
       </c>
       <c r="I3">
-        <v>0.005068407368045264</v>
+        <v>0.003577759706707618</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -665,28 +665,28 @@
         <v>31</v>
       </c>
       <c r="M3">
-        <v>0.2019839570023267</v>
+        <v>0.2036201992634756</v>
       </c>
       <c r="N3">
-        <v>-0.1557643802749924</v>
+        <v>0.5278061963378733</v>
       </c>
       <c r="O3">
-        <v>0.433086469010683</v>
+        <v>0.4604090806316603</v>
       </c>
       <c r="P3">
-        <v>0.577942445712702</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.1420784172480873</v>
+        <v>0.3278115574106878</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.8196537079418696</v>
       </c>
       <c r="S3">
-        <v>0.2077088020403448</v>
+        <v>0.2901414062795252</v>
       </c>
       <c r="T3">
-        <v>-0.1539621060846857</v>
+        <v>-0.2001796380769411</v>
       </c>
       <c r="U3">
         <v>2</v>
@@ -695,10 +695,10 @@
         <v>32</v>
       </c>
       <c r="W3">
-        <v>99.68909798485711</v>
+        <v>55.54229810662171</v>
       </c>
       <c r="X3">
-        <v>0.1016014908011649</v>
+        <v>0.1381427602223094</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -706,28 +706,28 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>1139</v>
+        <v>890</v>
       </c>
       <c r="C4">
-        <v>16544740.35864704</v>
+        <v>12752907.34577825</v>
       </c>
       <c r="D4">
-        <v>81638.20659304732</v>
+        <v>34882.611540844</v>
       </c>
       <c r="E4">
-        <v>0.005109577392926078</v>
+        <v>0.003022402970105342</v>
       </c>
       <c r="F4">
-        <v>0.6873676359846619</v>
+        <v>0.6909440643754788</v>
       </c>
       <c r="G4">
-        <v>1.377524143985953</v>
+        <v>1.265168539325843</v>
       </c>
       <c r="H4">
-        <v>0.1468630698188813</v>
+        <v>0.1132159566455185</v>
       </c>
       <c r="I4">
-        <v>0.004934390315190376</v>
+        <v>0.00273526738609856</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -739,28 +739,28 @@
         <v>31</v>
       </c>
       <c r="M4">
-        <v>0.2042036651359909</v>
+        <v>0.2007193697276898</v>
       </c>
       <c r="N4">
-        <v>0.5278061963378733</v>
+        <v>0.3884548653240452</v>
       </c>
       <c r="O4">
-        <v>0.4333117911035017</v>
+        <v>0.2896651138078312</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.7450174454296572</v>
       </c>
       <c r="Q4">
-        <v>0.3277069999231312</v>
+        <v>0.09753378041959387</v>
       </c>
       <c r="R4">
-        <v>0.8196537079418696</v>
+        <v>0.6525607418606123</v>
       </c>
       <c r="S4">
-        <v>0.345491861554974</v>
+        <v>0.07225106380775075</v>
       </c>
       <c r="T4">
-        <v>-0.1767844954891333</v>
+        <v>-0.2750077544661121</v>
       </c>
       <c r="U4">
         <v>3</v>
@@ -769,10 +769,10 @@
         <v>33</v>
       </c>
       <c r="W4">
-        <v>92.00161649788313</v>
+        <v>33.91927436762389</v>
       </c>
       <c r="X4">
-        <v>0.1213332687825967</v>
+        <v>0.08140917362035714</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -780,28 +780,28 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>1972</v>
+        <v>976</v>
       </c>
       <c r="C5">
-        <v>27615980.29119994</v>
+        <v>13488381.37391186</v>
       </c>
       <c r="D5">
-        <v>148883.5101809135</v>
+        <v>94422.09484959475</v>
       </c>
       <c r="E5">
-        <v>0.005786475883708949</v>
+        <v>0.006232861936331147</v>
       </c>
       <c r="F5">
-        <v>0.6895968543224502</v>
+        <v>0.6905296766388008</v>
       </c>
       <c r="G5">
-        <v>1.342292089249493</v>
+        <v>1.450819672131147</v>
       </c>
       <c r="H5">
-        <v>0.2451393949802069</v>
+        <v>0.1197452439229522</v>
       </c>
       <c r="I5">
-        <v>0.005391208590497017</v>
+        <v>0.007000253939454762</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -813,28 +813,28 @@
         <v>31</v>
       </c>
       <c r="M5">
-        <v>0.2147479007159943</v>
+        <v>0.2025736044945878</v>
       </c>
       <c r="N5">
-        <v>0.5685714536837877</v>
+        <v>-0.1557643802749924</v>
       </c>
       <c r="O5">
-        <v>0.5313870571669315</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>0.5211313340700503</v>
+        <v>0.6652290723023007</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.1422023696992656</v>
       </c>
       <c r="R5">
-        <v>0.8685343875409663</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0.2115284130619332</v>
       </c>
       <c r="T5">
-        <v>-0.1912966225333854</v>
+        <v>-0.307656192381655</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -843,10 +843,10 @@
         <v>33</v>
       </c>
       <c r="W5">
-        <v>87.1133593565182</v>
+        <v>24.484880156531</v>
       </c>
       <c r="X5">
-        <v>0.2212753527049638</v>
+        <v>0.2203626498608912</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -854,28 +854,28 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>1271</v>
+        <v>809</v>
       </c>
       <c r="C6">
-        <v>17742449.14435855</v>
+        <v>11147001.19290712</v>
       </c>
       <c r="D6">
-        <v>95963.44596080088</v>
+        <v>49601.3950815514</v>
       </c>
       <c r="E6">
-        <v>0.005350834438460387</v>
+        <v>0.004945577544790887</v>
       </c>
       <c r="F6">
-        <v>0.6897019629952355</v>
+        <v>0.6894165745275845</v>
       </c>
       <c r="G6">
-        <v>1.313139260424862</v>
+        <v>1.316440049443758</v>
       </c>
       <c r="H6">
-        <v>0.1574947984048608</v>
+        <v>0.09895927019351372</v>
       </c>
       <c r="I6">
-        <v>0.005408692181108138</v>
+        <v>0.004449752379421378</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -887,28 +887,28 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>0.2058302062149173</v>
+        <v>0.1997574729427846</v>
       </c>
       <c r="N6">
-        <v>0.6782104678706893</v>
+        <v>0.2849365059618074</v>
       </c>
       <c r="O6">
-        <v>0.4682673261691638</v>
+        <v>0.7151799722777107</v>
       </c>
       <c r="P6">
-        <v>0.5457029168272812</v>
+        <v>0.4509065943000549</v>
       </c>
       <c r="Q6">
-        <v>0.4004369956300114</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0.5284342653938368</v>
       </c>
       <c r="S6">
-        <v>0.4464554985673522</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>-0.2750511688406791</v>
+        <v>-0.3256961220235114</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -917,10 +917,10 @@
         <v>33</v>
       </c>
       <c r="W6">
-        <v>58.901522603713</v>
+        <v>19.27189544277756</v>
       </c>
       <c r="X6">
-        <v>0.1426238898180018</v>
+        <v>0.1157599275294468</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -928,28 +928,28 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>890</v>
+        <v>1271</v>
       </c>
       <c r="C7">
-        <v>12753198.85762022</v>
+        <v>17738299.12155825</v>
       </c>
       <c r="D7">
-        <v>119373.1685739635</v>
+        <v>94367.40951191924</v>
       </c>
       <c r="E7">
-        <v>0.008200570620167135</v>
+        <v>0.004872875091881172</v>
       </c>
       <c r="F7">
-        <v>0.6916452876859673</v>
+        <v>0.6900363533654161</v>
       </c>
       <c r="G7">
-        <v>1.560674157303371</v>
+        <v>1.280881195908733</v>
       </c>
       <c r="H7">
-        <v>0.1132066078789718</v>
+        <v>0.1574745624554699</v>
       </c>
       <c r="I7">
-        <v>0.009360253055462731</v>
+        <v>0.005319980730127037</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -961,28 +961,28 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>0.2029299465731575</v>
+        <v>0.2057038769553827</v>
       </c>
       <c r="N7">
-        <v>0.3884548653240452</v>
+        <v>0.6782104678706893</v>
       </c>
       <c r="O7">
-        <v>0.8811632596616841</v>
+        <v>0.6990940826411192</v>
       </c>
       <c r="P7">
+        <v>0.5702420398076313</v>
+      </c>
+      <c r="Q7">
+        <v>0.4003186635182989</v>
+      </c>
+      <c r="R7">
         <v>1</v>
       </c>
-      <c r="Q7">
-        <v>0.09746839736639851</v>
-      </c>
-      <c r="R7">
-        <v>0.6525607418606123</v>
-      </c>
       <c r="S7">
-        <v>0.2664288361570978</v>
+        <v>0.4466529283422783</v>
       </c>
       <c r="T7">
-        <v>-0.4028665349523433</v>
+        <v>-0.3363617476564859</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -991,10 +991,10 @@
         <v>34</v>
       </c>
       <c r="W7">
-        <v>15.84826278409318</v>
+        <v>16.18985773580615</v>
       </c>
       <c r="X7">
-        <v>0.1774161554064376</v>
+        <v>0.2202350250084887</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1005,25 +1005,25 @@
         <v>943</v>
       </c>
       <c r="C8">
-        <v>13361890.28490731</v>
+        <v>13359135.74845482</v>
       </c>
       <c r="D8">
-        <v>138201.7092190425</v>
+        <v>49329.10970550036</v>
       </c>
       <c r="E8">
-        <v>0.009020761208613131</v>
+        <v>0.003953842396188018</v>
       </c>
       <c r="F8">
-        <v>0.6909876265486031</v>
+        <v>0.6922683380702455</v>
       </c>
       <c r="G8">
-        <v>1.542948038176034</v>
+        <v>1.250265111346766</v>
       </c>
       <c r="H8">
-        <v>0.1186097927973194</v>
+        <v>0.1185978453940032</v>
       </c>
       <c r="I8">
-        <v>0.01034297590178134</v>
+        <v>0.003692537499007449</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1035,28 +1035,28 @@
         <v>31</v>
       </c>
       <c r="M8">
-        <v>0.2036668090728978</v>
+        <v>0.2018949891119246</v>
       </c>
       <c r="N8">
         <v>0.6585491754669682</v>
       </c>
       <c r="O8">
+        <v>0.4957521330414547</v>
+      </c>
+      <c r="P8">
         <v>1</v>
       </c>
-      <c r="P8">
-        <v>0.8462565016306721</v>
-      </c>
       <c r="Q8">
-        <v>0.1344307419876795</v>
+        <v>0.1343527114667572</v>
       </c>
       <c r="R8">
         <v>0.9764245978791358</v>
       </c>
       <c r="S8">
-        <v>0.3121678088247439</v>
+        <v>0.160555497793735</v>
       </c>
       <c r="T8">
-        <v>-0.4499164335772</v>
+        <v>-0.3923879803241271</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0.2053997243530389</v>
+        <v>0.1151244668665527</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_attractiveness.xlsx
+++ b/data/outputs/sector_attractiveness.xlsx
@@ -564,7 +564,7 @@
         <v>27612128.92570351</v>
       </c>
       <c r="D2">
-        <v>46690.29756361964</v>
+        <v>54305.71518045494</v>
       </c>
       <c r="E2">
         <v>0.001713220526860417</v>
@@ -573,13 +573,13 @@
         <v>0.6893616691836554</v>
       </c>
       <c r="G2">
-        <v>1.269269776876268</v>
+        <v>1.308316430020284</v>
       </c>
       <c r="H2">
         <v>0.2451310518128871</v>
       </c>
       <c r="I2">
-        <v>0.001690934360376562</v>
+        <v>0.001966734087276515</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>100</v>
       </c>
       <c r="X2">
-        <v>0.1089659968919541</v>
+        <v>0.1161650031830108</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -638,7 +638,7 @@
         <v>16544460.35796101</v>
       </c>
       <c r="D3">
-        <v>59192.10363793441</v>
+        <v>66660.95808633778</v>
       </c>
       <c r="E3">
         <v>0.003794104472979617</v>
@@ -647,13 +647,13 @@
         <v>0.687074752583591</v>
       </c>
       <c r="G3">
-        <v>1.287093942054434</v>
+        <v>1.294117647058824</v>
       </c>
       <c r="H3">
         <v>0.1468760695756554</v>
       </c>
       <c r="I3">
-        <v>0.003577759706707618</v>
+        <v>0.004029201112882552</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>55.54229810662171</v>
       </c>
       <c r="X3">
-        <v>0.1381427602223094</v>
+        <v>0.1425940231622064</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -712,7 +712,7 @@
         <v>12752907.34577825</v>
       </c>
       <c r="D4">
-        <v>34882.611540844</v>
+        <v>39793.7704862884</v>
       </c>
       <c r="E4">
         <v>0.003022402970105342</v>
@@ -721,13 +721,13 @@
         <v>0.6909440643754788</v>
       </c>
       <c r="G4">
-        <v>1.265168539325843</v>
+        <v>1.29438202247191</v>
       </c>
       <c r="H4">
         <v>0.1132159566455185</v>
       </c>
       <c r="I4">
-        <v>0.00273526738609856</v>
+        <v>0.003120368509496136</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>33.91927436762389</v>
       </c>
       <c r="X4">
-        <v>0.08140917362035714</v>
+        <v>0.08512259639418979</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -786,7 +786,7 @@
         <v>13488381.37391186</v>
       </c>
       <c r="D5">
-        <v>94422.09484959475</v>
+        <v>95684.50570900874</v>
       </c>
       <c r="E5">
         <v>0.006232861936331147</v>
@@ -795,13 +795,13 @@
         <v>0.6905296766388008</v>
       </c>
       <c r="G5">
-        <v>1.450819672131147</v>
+        <v>1.29405737704918</v>
       </c>
       <c r="H5">
         <v>0.1197452439229522</v>
       </c>
       <c r="I5">
-        <v>0.007000253939454762</v>
+        <v>0.007093846404289396</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>24.484880156531</v>
       </c>
       <c r="X5">
-        <v>0.2203626498608912</v>
+        <v>0.2046781056711368</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -860,7 +860,7 @@
         <v>11147001.19290712</v>
       </c>
       <c r="D6">
-        <v>49601.3950815514</v>
+        <v>53082.42027069654</v>
       </c>
       <c r="E6">
         <v>0.004945577544790887</v>
@@ -869,13 +869,13 @@
         <v>0.6894165745275845</v>
       </c>
       <c r="G6">
-        <v>1.316440049443758</v>
+        <v>1.273176761433869</v>
       </c>
       <c r="H6">
         <v>0.09895927019351372</v>
       </c>
       <c r="I6">
-        <v>0.004449752379421378</v>
+        <v>0.004762035937026102</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>19.27189544277756</v>
       </c>
       <c r="X6">
-        <v>0.1157599275294468</v>
+        <v>0.1135482609743198</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -934,7 +934,7 @@
         <v>17738299.12155825</v>
       </c>
       <c r="D7">
-        <v>94367.40951191924</v>
+        <v>101660.7505560984</v>
       </c>
       <c r="E7">
         <v>0.004872875091881172</v>
@@ -943,13 +943,13 @@
         <v>0.6900363533654161</v>
       </c>
       <c r="G7">
-        <v>1.280881195908733</v>
+        <v>1.265932336742722</v>
       </c>
       <c r="H7">
         <v>0.1574745624554699</v>
       </c>
       <c r="I7">
-        <v>0.005319980730127037</v>
+        <v>0.0057311442241125</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>16.18985773580615</v>
       </c>
       <c r="X7">
-        <v>0.2202350250084887</v>
+        <v>0.2174618522690359</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1008,7 +1008,7 @@
         <v>13359135.74845482</v>
       </c>
       <c r="D8">
-        <v>49329.10970550036</v>
+        <v>56299.62294217812</v>
       </c>
       <c r="E8">
         <v>0.003953842396188018</v>
@@ -1017,13 +1017,13 @@
         <v>0.6922683380702455</v>
       </c>
       <c r="G8">
-        <v>1.250265111346766</v>
+        <v>1.277836691410392</v>
       </c>
       <c r="H8">
         <v>0.1185978453940032</v>
       </c>
       <c r="I8">
-        <v>0.003692537499007449</v>
+        <v>0.004214316255352821</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0.1151244668665527</v>
+        <v>0.1204301583461006</v>
       </c>
     </row>
   </sheetData>
